--- a/Config/Datas/Tables/j_技能_SkillConfig.xlsx
+++ b/Config/Datas/Tables/j_技能_SkillConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSkill" sheetId="1" r:id="R9a919821b74947a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSkill" sheetId="1" r:id="R195cec0d86e248ad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1654,7 +1654,7 @@
         <x:v>20001</x:v>
       </x:c>
       <x:c r="C5" s="40" t="str">
-        <x:v>skill_1</x:v>
+        <x:v>追星飞刃</x:v>
       </x:c>
       <x:c r="D5" s="71" t="n">
         <x:v>30002</x:v>
@@ -1685,7 +1685,7 @@
       <x:c r="N5" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O5">
+      <x:c r="O5" t="n">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="P5" t="n">
@@ -1694,9 +1694,12 @@
       <x:c r="Q5" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R5">
+      <x:c r="R5" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="S5"/>
+      <x:c r="T5"/>
+      <x:c r="U5"/>
     </x:row>
     <x:row r="6" ht="14.5">
       <x:c r="A6" s="40"/>
@@ -1793,28 +1796,40 @@
         <x:v>20007</x:v>
       </x:c>
       <x:c r="C9" s="40" t="str">
-        <x:v>skill_7</x:v>
+        <x:v>玄冰天阵</x:v>
       </x:c>
       <x:c r="D9" s="71" t="n">
         <x:v>30006</x:v>
       </x:c>
-      <x:c r="E9" s="40"/>
+      <x:c r="E9" s="40" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="F9" s="40"/>
       <x:c r="G9" s="40"/>
       <x:c r="H9" s="40"/>
       <x:c r="I9" s="40"/>
       <x:c r="J9" s="40"/>
-      <x:c r="K9" s="40"/>
-      <x:c r="L9" s="40"/>
+      <x:c r="K9" s="40" t="str">
+        <x:v>30055</x:v>
+      </x:c>
+      <x:c r="L9" s="40" t="n">
+        <x:v>200</x:v>
+      </x:c>
       <x:c r="M9"/>
       <x:c r="N9"/>
       <x:c r="O9"/>
       <x:c r="P9"/>
       <x:c r="Q9"/>
       <x:c r="R9"/>
-      <x:c r="S9"/>
-      <x:c r="T9"/>
-      <x:c r="U9"/>
+      <x:c r="S9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U9" t="n">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="14.5">
       <x:c r="A10" s="40"/>
@@ -1996,13 +2011,13 @@
         <x:v>20014</x:v>
       </x:c>
       <x:c r="C16" s="40" t="str">
-        <x:v>skill_14</x:v>
+        <x:v>焚天炎符</x:v>
       </x:c>
       <x:c r="D16" s="71" t="n">
         <x:v>30013</x:v>
       </x:c>
       <x:c r="E16" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F16" s="40" t="n">
         <x:v>50</x:v>
@@ -2027,7 +2042,7 @@
       <x:c r="N16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O16">
+      <x:c r="O16" t="n">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="P16" t="n">
@@ -2036,9 +2051,12 @@
       <x:c r="Q16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R16">
+      <x:c r="R16" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="S16"/>
+      <x:c r="T16"/>
+      <x:c r="U16"/>
     </x:row>
     <x:row r="17" ht="14.5">
       <x:c r="A17" s="40"/>
@@ -2075,25 +2093,49 @@
         <x:v>20016</x:v>
       </x:c>
       <x:c r="C18" s="40" t="str">
-        <x:v>skill_16</x:v>
+        <x:v>连锁灵梭</x:v>
       </x:c>
       <x:c r="D18" s="71" t="n">
         <x:v>30015</x:v>
       </x:c>
-      <x:c r="E18" s="40"/>
-      <x:c r="F18" s="40"/>
-      <x:c r="G18" s="40"/>
-      <x:c r="H18" s="40"/>
-      <x:c r="I18" s="40"/>
-      <x:c r="J18" s="40"/>
+      <x:c r="E18" s="40" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F18" s="40" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G18" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="40" t="n">
+        <x:v>30029</x:v>
+      </x:c>
+      <x:c r="J18" s="40" t="n">
+        <x:v>30030</x:v>
+      </x:c>
       <x:c r="K18" s="40"/>
       <x:c r="L18" s="40"/>
-      <x:c r="M18"/>
-      <x:c r="N18"/>
-      <x:c r="O18"/>
-      <x:c r="P18"/>
-      <x:c r="Q18"/>
-      <x:c r="R18"/>
+      <x:c r="M18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="P18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R18" t="n">
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="S18"/>
       <x:c r="T18"/>
       <x:c r="U18"/>
@@ -2394,25 +2436,49 @@
         <x:v>20027</x:v>
       </x:c>
       <x:c r="C29" s="40" t="str">
-        <x:v>skill_27</x:v>
+        <x:v>焚天龙符</x:v>
       </x:c>
       <x:c r="D29" s="71" t="n">
         <x:v>30026</x:v>
       </x:c>
-      <x:c r="E29" s="40"/>
-      <x:c r="F29" s="40"/>
-      <x:c r="G29" s="40"/>
-      <x:c r="H29" s="40"/>
-      <x:c r="I29" s="40"/>
-      <x:c r="J29" s="40"/>
+      <x:c r="E29" s="40" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F29" s="40" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="40" t="n">
+        <x:v>30042</x:v>
+      </x:c>
+      <x:c r="J29" s="40" t="n">
+        <x:v>30043</x:v>
+      </x:c>
       <x:c r="K29" s="40"/>
       <x:c r="L29" s="40"/>
-      <x:c r="M29"/>
-      <x:c r="N29"/>
-      <x:c r="O29"/>
-      <x:c r="P29"/>
-      <x:c r="Q29"/>
-      <x:c r="R29"/>
+      <x:c r="M29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O29" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="P29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R29" t="n">
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="S29"/>
       <x:c r="T29"/>
       <x:c r="U29"/>
@@ -2423,7 +2489,7 @@
         <x:v>20028</x:v>
       </x:c>
       <x:c r="C30" s="40" t="str">
-        <x:v>skill_28</x:v>
+        <x:v>落雷法印</x:v>
       </x:c>
       <x:c r="D30" s="71" t="n">
         <x:v>30027</x:v>
@@ -2442,13 +2508,19 @@
       <x:c r="L30" s="40" t="n">
         <x:v>50</x:v>
       </x:c>
+      <x:c r="M30"/>
+      <x:c r="N30"/>
+      <x:c r="O30"/>
+      <x:c r="P30"/>
+      <x:c r="Q30"/>
+      <x:c r="R30"/>
       <x:c r="S30" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T30" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U30">
+      <x:c r="U30" t="n">
         <x:v>1000</x:v>
       </x:c>
     </x:row>
@@ -2487,25 +2559,49 @@
         <x:v>20030</x:v>
       </x:c>
       <x:c r="C32" s="40" t="str">
-        <x:v>skill_30</x:v>
+        <x:v>御龙连梭</x:v>
       </x:c>
       <x:c r="D32" s="71" t="n">
         <x:v>30029</x:v>
       </x:c>
-      <x:c r="E32" s="40"/>
-      <x:c r="F32" s="40"/>
-      <x:c r="G32" s="40"/>
-      <x:c r="H32" s="40"/>
-      <x:c r="I32" s="40"/>
-      <x:c r="J32" s="40"/>
+      <x:c r="E32" s="40" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F32" s="40" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G32" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I32" s="40" t="n">
+        <x:v>30047</x:v>
+      </x:c>
+      <x:c r="J32" s="40" t="n">
+        <x:v>30048</x:v>
+      </x:c>
       <x:c r="K32" s="40"/>
       <x:c r="L32" s="40"/>
-      <x:c r="M32"/>
-      <x:c r="N32"/>
-      <x:c r="O32"/>
-      <x:c r="P32"/>
-      <x:c r="Q32"/>
-      <x:c r="R32"/>
+      <x:c r="M32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O32" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="P32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R32" t="n">
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="S32"/>
       <x:c r="T32"/>
       <x:c r="U32"/>
@@ -2576,7 +2672,7 @@
       <x:c r="N34" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O34">
+      <x:c r="O34" t="n">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="P34" t="n">
@@ -2585,9 +2681,12 @@
       <x:c r="Q34" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R34">
+      <x:c r="R34" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="S34"/>
+      <x:c r="T34"/>
+      <x:c r="U34"/>
     </x:row>
     <x:row r="35" ht="14.5">
       <x:c r="A35" s="40"/>
@@ -2595,28 +2694,40 @@
         <x:v>20033</x:v>
       </x:c>
       <x:c r="C35" s="40" t="str">
-        <x:v>skill_33</x:v>
+        <x:v>寒霜灵阵</x:v>
       </x:c>
       <x:c r="D35" s="71" t="n">
         <x:v>30032</x:v>
       </x:c>
-      <x:c r="E35" s="40"/>
+      <x:c r="E35" s="40" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="F35" s="40"/>
       <x:c r="G35" s="40"/>
       <x:c r="H35" s="40"/>
       <x:c r="I35" s="40"/>
       <x:c r="J35" s="40"/>
-      <x:c r="K35" s="40"/>
-      <x:c r="L35" s="40"/>
+      <x:c r="K35" s="40" t="str">
+        <x:v>30055</x:v>
+      </x:c>
+      <x:c r="L35" s="40" t="n">
+        <x:v>120</x:v>
+      </x:c>
       <x:c r="M35"/>
       <x:c r="N35"/>
       <x:c r="O35"/>
       <x:c r="P35"/>
       <x:c r="Q35"/>
       <x:c r="R35"/>
-      <x:c r="S35"/>
-      <x:c r="T35"/>
-      <x:c r="U35"/>
+      <x:c r="S35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U35" t="n">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="14.5">
       <x:c r="A36" s="40"/>
@@ -2624,28 +2735,40 @@
         <x:v>20037</x:v>
       </x:c>
       <x:c r="C36" s="40" t="str">
-        <x:v>skill_37</x:v>
+        <x:v>不灭罡域</x:v>
       </x:c>
       <x:c r="D36" s="71" t="n">
         <x:v>30033</x:v>
       </x:c>
-      <x:c r="E36" s="40"/>
+      <x:c r="E36" s="40" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="F36" s="40"/>
       <x:c r="G36" s="40"/>
       <x:c r="H36" s="40"/>
       <x:c r="I36" s="40"/>
       <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
+      <x:c r="K36" s="40" t="str">
+        <x:v>30065</x:v>
+      </x:c>
+      <x:c r="L36" s="40" t="n">
+        <x:v>160</x:v>
+      </x:c>
       <x:c r="M36"/>
       <x:c r="N36"/>
       <x:c r="O36"/>
       <x:c r="P36"/>
       <x:c r="Q36"/>
       <x:c r="R36"/>
-      <x:c r="S36"/>
-      <x:c r="T36"/>
-      <x:c r="U36"/>
+      <x:c r="S36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U36" t="n">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="14.5">
       <x:c r="A37" s="40"/>
@@ -2798,13 +2921,13 @@
         <x:v>20043</x:v>
       </x:c>
       <x:c r="C42" s="40" t="str">
-        <x:v>skill_43</x:v>
+        <x:v>护体罡环</x:v>
       </x:c>
       <x:c r="D42" s="71" t="n">
         <x:v>30039</x:v>
       </x:c>
       <x:c r="E42" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F42" s="40"/>
       <x:c r="G42" s="40"/>
@@ -2817,13 +2940,19 @@
       <x:c r="L42" s="40" t="n">
         <x:v>50</x:v>
       </x:c>
+      <x:c r="M42"/>
+      <x:c r="N42"/>
+      <x:c r="O42"/>
+      <x:c r="P42"/>
+      <x:c r="Q42"/>
+      <x:c r="R42"/>
       <x:c r="S42" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T42" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U42">
+      <x:c r="U42" t="n">
         <x:v>1000</x:v>
       </x:c>
     </x:row>
@@ -2833,25 +2962,49 @@
         <x:v>20044</x:v>
       </x:c>
       <x:c r="C43" s="40" t="str">
-        <x:v>skill_44</x:v>
+        <x:v>万象星羽</x:v>
       </x:c>
       <x:c r="D43" s="71" t="n">
         <x:v>30040</x:v>
       </x:c>
-      <x:c r="E43" s="40"/>
-      <x:c r="F43" s="40"/>
-      <x:c r="G43" s="40"/>
-      <x:c r="H43" s="40"/>
-      <x:c r="I43" s="40"/>
-      <x:c r="J43" s="40"/>
+      <x:c r="E43" s="40" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F43" s="40" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G43" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I43" s="40" t="n">
+        <x:v>30067</x:v>
+      </x:c>
+      <x:c r="J43" s="40" t="n">
+        <x:v>30068</x:v>
+      </x:c>
       <x:c r="K43" s="40"/>
       <x:c r="L43" s="40"/>
-      <x:c r="M43"/>
-      <x:c r="N43"/>
-      <x:c r="O43"/>
-      <x:c r="P43"/>
-      <x:c r="Q43"/>
-      <x:c r="R43"/>
+      <x:c r="M43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O43" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="P43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R43" t="n">
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="S43"/>
       <x:c r="T43"/>
       <x:c r="U43"/>
@@ -2949,28 +3102,40 @@
         <x:v>20050</x:v>
       </x:c>
       <x:c r="C47" s="40" t="str">
-        <x:v>skill_50</x:v>
+        <x:v>九霄雷劫</x:v>
       </x:c>
       <x:c r="D47" s="71" t="n">
         <x:v>30044</x:v>
       </x:c>
-      <x:c r="E47" s="40"/>
+      <x:c r="E47" s="40" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="F47" s="40"/>
       <x:c r="G47" s="40"/>
       <x:c r="H47" s="40"/>
       <x:c r="I47" s="40"/>
       <x:c r="J47" s="40"/>
-      <x:c r="K47" s="40"/>
-      <x:c r="L47" s="40"/>
+      <x:c r="K47" s="40" t="str">
+        <x:v>30063</x:v>
+      </x:c>
+      <x:c r="L47" s="40" t="n">
+        <x:v>160</x:v>
+      </x:c>
       <x:c r="M47"/>
       <x:c r="N47"/>
       <x:c r="O47"/>
       <x:c r="P47"/>
       <x:c r="Q47"/>
       <x:c r="R47"/>
-      <x:c r="S47"/>
-      <x:c r="T47"/>
-      <x:c r="U47"/>
+      <x:c r="S47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U47" t="n">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="14.5">
       <x:c r="A48" s="40"/>
@@ -4422,6 +4587,68 @@
       <x:c r="T97"/>
       <x:c r="U97"/>
     </x:row>
+    <x:row r="98">
+      <x:c r="A98"/>
+      <x:c r="B98" t="n">
+        <x:v>29001</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>迅影突袭</x:v>
+      </x:c>
+      <x:c r="D98" t="n">
+        <x:v>30003</x:v>
+      </x:c>
+      <x:c r="E98" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F98"/>
+      <x:c r="G98"/>
+      <x:c r="H98"/>
+      <x:c r="I98"/>
+      <x:c r="J98"/>
+      <x:c r="K98"/>
+      <x:c r="L98"/>
+      <x:c r="M98"/>
+      <x:c r="N98"/>
+      <x:c r="O98"/>
+      <x:c r="P98"/>
+      <x:c r="Q98"/>
+      <x:c r="R98"/>
+      <x:c r="S98"/>
+      <x:c r="T98"/>
+      <x:c r="U98"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99"/>
+      <x:c r="B99" t="n">
+        <x:v>29002</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>镇域重击</x:v>
+      </x:c>
+      <x:c r="D99" t="n">
+        <x:v>30003</x:v>
+      </x:c>
+      <x:c r="E99" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F99"/>
+      <x:c r="G99"/>
+      <x:c r="H99"/>
+      <x:c r="I99"/>
+      <x:c r="J99"/>
+      <x:c r="K99"/>
+      <x:c r="L99"/>
+      <x:c r="M99"/>
+      <x:c r="N99"/>
+      <x:c r="O99"/>
+      <x:c r="P99"/>
+      <x:c r="Q99"/>
+      <x:c r="R99"/>
+      <x:c r="S99"/>
+      <x:c r="T99"/>
+      <x:c r="U99"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Config/Datas/Tables/j_技能_SkillConfig.xlsx
+++ b/Config/Datas/Tables/j_技能_SkillConfig.xlsx
@@ -1426,6 +1426,7 @@
     <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="26" hidden="0" customWidth="1"/>
+    <x:col min="22" max="25" width="32" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -1492,6 +1493,18 @@
       <x:c r="U1" t="str">
         <x:v>areaVisualScalePermille</x:v>
       </x:c>
+      <x:c r="V1" t="str">
+        <x:v>castClipId</x:v>
+      </x:c>
+      <x:c r="W1" t="str">
+        <x:v>castVisualOffsetXPixels</x:v>
+      </x:c>
+      <x:c r="X1" t="str">
+        <x:v>castVisualOffsetYPixels</x:v>
+      </x:c>
+      <x:c r="Y1" t="str">
+        <x:v>castVisualScalePermille</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="53" t="str">
@@ -1555,6 +1568,18 @@
         <x:v>float?</x:v>
       </x:c>
       <x:c r="U2" t="str">
+        <x:v>int?</x:v>
+      </x:c>
+      <x:c r="V2" t="str">
+        <x:v>int?#ref=TbAnimationClip</x:v>
+      </x:c>
+      <x:c r="W2" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="X2" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="Y2" t="str">
         <x:v>int?</x:v>
       </x:c>
     </x:row>
@@ -1647,6 +1672,18 @@
       <x:c r="U4" t="str">
         <x:v>范围特效表现相对缩放（千分比）；由技能预制体“范围特效表现”节点统一 Scale 导出。</x:v>
       </x:c>
+      <x:c r="V4" t="str">
+        <x:v>随身施法片段（不阻塞发射）</x:v>
+      </x:c>
+      <x:c r="W4" t="str">
+        <x:v>随身层相对施法者根节点X像素偏移</x:v>
+      </x:c>
+      <x:c r="X4" t="str">
+        <x:v>随身层相对施法者根节点Y像素偏移</x:v>
+      </x:c>
+      <x:c r="Y4" t="str">
+        <x:v>随身层视觉缩放千分比</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="14.5">
       <x:c r="A5" s="40"/>
@@ -1700,6 +1737,18 @@
       <x:c r="S5"/>
       <x:c r="T5"/>
       <x:c r="U5"/>
+      <x:c r="V5" t="n">
+        <x:v>30004</x:v>
+      </x:c>
+      <x:c r="W5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y5" t="n">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="14.5">
       <x:c r="A6" s="40"/>
@@ -2111,10 +2160,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="40" t="n">
-        <x:v>30029</x:v>
+        <x:v>30051</x:v>
       </x:c>
       <x:c r="J18" s="40" t="n">
-        <x:v>30030</x:v>
+        <x:v>30052</x:v>
       </x:c>
       <x:c r="K18" s="40"/>
       <x:c r="L18" s="40"/>
@@ -2139,6 +2188,18 @@
       <x:c r="S18"/>
       <x:c r="T18"/>
       <x:c r="U18"/>
+      <x:c r="V18" t="n">
+        <x:v>30053</x:v>
+      </x:c>
+      <x:c r="W18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y18" t="n">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="14.5">
       <x:c r="A19" s="40"/>
@@ -2482,6 +2543,18 @@
       <x:c r="S29"/>
       <x:c r="T29"/>
       <x:c r="U29"/>
+      <x:c r="V29" t="n">
+        <x:v>30044</x:v>
+      </x:c>
+      <x:c r="W29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y29" t="n">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="14.5">
       <x:c r="A30" s="40"/>
@@ -2577,10 +2650,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="40" t="n">
-        <x:v>30047</x:v>
+        <x:v>30077</x:v>
       </x:c>
       <x:c r="J32" s="40" t="n">
-        <x:v>30048</x:v>
+        <x:v>30078</x:v>
       </x:c>
       <x:c r="K32" s="40"/>
       <x:c r="L32" s="40"/>
@@ -2605,6 +2678,18 @@
       <x:c r="S32"/>
       <x:c r="T32"/>
       <x:c r="U32"/>
+      <x:c r="V32" t="n">
+        <x:v>30079</x:v>
+      </x:c>
+      <x:c r="W32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y32" t="n">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="14.5">
       <x:c r="A33" s="40"/>
@@ -2687,6 +2772,18 @@
       <x:c r="S34"/>
       <x:c r="T34"/>
       <x:c r="U34"/>
+      <x:c r="V34" t="n">
+        <x:v>30053</x:v>
+      </x:c>
+      <x:c r="W34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y34" t="n">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="14.5">
       <x:c r="A35" s="40"/>
@@ -2749,7 +2846,7 @@
       <x:c r="I36" s="40"/>
       <x:c r="J36" s="40"/>
       <x:c r="K36" s="40" t="str">
-        <x:v>30065</x:v>
+        <x:v>30097</x:v>
       </x:c>
       <x:c r="L36" s="40" t="n">
         <x:v>160</x:v>
@@ -2935,7 +3032,7 @@
       <x:c r="I42" s="40"/>
       <x:c r="J42" s="40"/>
       <x:c r="K42" s="40" t="str">
-        <x:v>30063;30064;30065</x:v>
+        <x:v>30097</x:v>
       </x:c>
       <x:c r="L42" s="40" t="n">
         <x:v>50</x:v>
@@ -3008,6 +3105,18 @@
       <x:c r="S43"/>
       <x:c r="T43"/>
       <x:c r="U43"/>
+      <x:c r="V43" t="n">
+        <x:v>30069</x:v>
+      </x:c>
+      <x:c r="W43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y43" t="n">
+        <x:v>1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="14.5">
       <x:c r="A44" s="40"/>
